--- a/Praktek Komputer - Spreadsheet/02- Fungsi Dasar Logika/02- Fungsi Dasar Logika.xlsx
+++ b/Praktek Komputer - Spreadsheet/02- Fungsi Dasar Logika/02- Fungsi Dasar Logika.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Yamin Folder\Praktek Komputer\Bahan Praktek\48 Rumus Excell\02- Fungsi Dasar Fungsi Logika\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\AY Labs\UIN Bukittinggi\Praktek Komputer\Prakom - Belajar Rumus Excell\02- Fungsi Dasar Logika\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6197271E-F5C2-4C76-A492-0EAFFA0C63E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5A6543E-FCA7-4E56-AF2A-8BB6F7A59F43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="900" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RUMUS" sheetId="10" r:id="rId1"/>
@@ -133,14 +133,6 @@
       <u/>
       <sz val="11"/>
       <color theme="10"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="16"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -205,8 +197,16 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -216,6 +216,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF009900"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -257,27 +263,27 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -285,6 +291,11 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FF009900"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -596,24 +607,24 @@
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.88671875" style="16" customWidth="1"/>
+    <col min="1" max="1" width="4.88671875" style="14" customWidth="1"/>
     <col min="2" max="2" width="20" style="2" customWidth="1"/>
     <col min="3" max="3" width="104" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="21" x14ac:dyDescent="0.4">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="14" t="s">
         <v>28</v>
       </c>
       <c r="B1" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="C1" s="14" t="s">
+      <c r="C1" s="16" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" s="16">
+      <c r="A2" s="14">
         <v>16</v>
       </c>
       <c r="B2" s="3" t="s">
@@ -624,7 +635,7 @@
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" s="16">
+      <c r="A3" s="14">
         <v>17</v>
       </c>
       <c r="B3" s="3" t="s">
@@ -635,7 +646,7 @@
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" s="16">
+      <c r="A4" s="14">
         <v>18</v>
       </c>
       <c r="B4" s="3" t="s">
@@ -709,10 +720,7 @@
       <c r="E4" s="10">
         <v>70</v>
       </c>
-      <c r="F4" s="8" t="str">
-        <f>IF(E4&gt;75,"Lulus","Tidak Lulus")</f>
-        <v>Tidak Lulus</v>
-      </c>
+      <c r="F4" s="8"/>
     </row>
     <row r="5" spans="1:6" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="C5" s="10">
@@ -724,10 +732,7 @@
       <c r="E5" s="10">
         <v>75</v>
       </c>
-      <c r="F5" s="8" t="str">
-        <f t="shared" ref="F5:F9" si="0">IF(E5&gt;75,"Lulus","Tidak Lulus")</f>
-        <v>Tidak Lulus</v>
-      </c>
+      <c r="F5" s="8"/>
     </row>
     <row r="6" spans="1:6" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="C6" s="10">
@@ -739,10 +744,7 @@
       <c r="E6" s="10">
         <v>81</v>
       </c>
-      <c r="F6" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v>Lulus</v>
-      </c>
+      <c r="F6" s="8"/>
     </row>
     <row r="7" spans="1:6" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="C7" s="10">
@@ -754,10 +756,7 @@
       <c r="E7" s="10">
         <v>73</v>
       </c>
-      <c r="F7" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v>Tidak Lulus</v>
-      </c>
+      <c r="F7" s="8"/>
     </row>
     <row r="8" spans="1:6" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="C8" s="10">
@@ -769,10 +768,7 @@
       <c r="E8" s="10">
         <v>81</v>
       </c>
-      <c r="F8" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v>Lulus</v>
-      </c>
+      <c r="F8" s="8"/>
     </row>
     <row r="9" spans="1:6" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="C9" s="10">
@@ -784,10 +780,7 @@
       <c r="E9" s="10">
         <v>80</v>
       </c>
-      <c r="F9" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v>Lulus</v>
-      </c>
+      <c r="F9" s="8"/>
     </row>
     <row r="10" spans="1:6" s="12" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="C10" s="13" t="s">
